--- a/06_方案乙_技术版/Demo/需知/tools/templates/需知_知识库填写模板.xlsx
+++ b/06_方案乙_技术版/Demo/需知/tools/templates/需知_知识库填写模板.xlsx
@@ -1655,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1664,12 +1664,14 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>系统目录 · 填写模板（黄色区域为填写区；第 3 行是示例，填写时覆盖或删除）</t>
+          <t>系统目录 · 填写模板（黄色区域为填写区；第 3 行是示例，填写时覆盖或删除）　｜　G、H 两列可选：数据域与接口，填了就有「数据地图」</t>
         </is>
       </c>
     </row>
@@ -1704,6 +1706,16 @@
           <t>成熟度（成熟/试点/改动受控）</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>数据域（名称:关键词/关键词:时效；分号分隔）</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>接口（名称:类型:状态；分号分隔）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1734,6 +1746,16 @@
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>成熟</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>报表数据集:报表/日报/周报/看板:日终</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>数据集配置 + 报表模板:配置:可用；订阅 / 定时分发任务:定时任务:可用</t>
         </is>
       </c>
     </row>
